--- a/Tier_RVR_Bootstrap_Comparison.xlsx
+++ b/Tier_RVR_Bootstrap_Comparison.xlsx
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.432870081076151</v>
+        <v>2.43287032058065</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5668296534420363</v>
+        <v>-0.5668353233227722</v>
       </c>
       <c r="E2" t="n">
-        <v>5.461728015505861</v>
+        <v>5.461732300806841</v>
       </c>
       <c r="F2" t="n">
         <v>0.1209596801066311</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2408329541657928</v>
+        <v>0.2408341513274592</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6036723525211319</v>
+        <v>-0.6036795522964437</v>
       </c>
       <c r="E3" t="n">
-        <v>1.104268089636279</v>
+        <v>1.104272985351038</v>
       </c>
       <c r="F3" t="n">
         <v>0.5911362879040319</v>
@@ -531,13 +531,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.104244610122322</v>
+        <v>0.104232455597975</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.624889850580461</v>
+        <v>-2.62490390569649</v>
       </c>
       <c r="E4" t="n">
-        <v>3.321403836030896</v>
+        <v>3.321389020570703</v>
       </c>
       <c r="F4" t="n">
         <v>0.9486837720759747</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.1398027947336986</v>
+        <v>-0.1398092980869468</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.356503856819461</v>
+        <v>-1.356512924378956</v>
       </c>
       <c r="E5" t="n">
-        <v>1.45936468633275</v>
+        <v>1.459362579304117</v>
       </c>
       <c r="F5" t="n">
         <v>0.8443852049316894</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02378929719447331</v>
+        <v>0.0237901608432361</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.949667887461475</v>
+        <v>-0.9496646598129518</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066741669199482</v>
+        <v>1.066747049794903</v>
       </c>
       <c r="F6" t="n">
         <v>0.9646784405198268</v>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36.14538543531631</v>
+        <v>36.14536798332978</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54608328634557</v>
+        <v>16.54608749320936</v>
       </c>
       <c r="E7" t="n">
-        <v>66.36938537326104</v>
+        <v>66.36935297151481</v>
       </c>
       <c r="F7" t="n">
         <v>0.01466177940686438</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.419807261401912</v>
+        <v>1.419797310508984</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.025300394508841</v>
+        <v>-2.025301551620312</v>
       </c>
       <c r="E8" t="n">
-        <v>5.445903836508562</v>
+        <v>5.445885507538816</v>
       </c>
       <c r="F8" t="n">
         <v>0.5071642785738087</v>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4935261758902425</v>
+        <v>0.493509991672418</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.570832771668376</v>
+        <v>-1.570845422389063</v>
       </c>
       <c r="E9" t="n">
-        <v>2.511998717646168</v>
+        <v>2.511980596846298</v>
       </c>
       <c r="F9" t="n">
         <v>0.6367877374208597</v>
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.885883770266992</v>
+        <v>1.885874753688674</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.667397976615858</v>
+        <v>-1.66741337588909</v>
       </c>
       <c r="E10" t="n">
-        <v>6.819760285062915</v>
+        <v>6.819756434585457</v>
       </c>
       <c r="F10" t="n">
         <v>0.3932022659113629</v>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.5968240947000811</v>
+        <v>-0.5968259561056602</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.712619329328031</v>
+        <v>-1.712625199242947</v>
       </c>
       <c r="E11" t="n">
-        <v>0.805123902688079</v>
+        <v>0.8051221142565057</v>
       </c>
       <c r="F11" t="n">
         <v>0.3475508163945352</v>
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33.71251535424016</v>
+        <v>33.71249766274914</v>
       </c>
       <c r="D12" t="n">
-        <v>15.23042475469797</v>
+        <v>15.23042407126197</v>
       </c>
       <c r="E12" t="n">
-        <v>63.542517916261</v>
+        <v>63.54243006577537</v>
       </c>
       <c r="F12" t="n">
         <v>0.01799400199933356</v>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.178974307236119</v>
+        <v>1.178963159181525</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.794786776452012</v>
+        <v>-1.794783401052814</v>
       </c>
       <c r="E13" t="n">
-        <v>4.61267540849247</v>
+        <v>4.612650427195579</v>
       </c>
       <c r="F13" t="n">
         <v>0.5041652782405864</v>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.3892815657679205</v>
+        <v>0.389277536074443</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.450555277878539</v>
+        <v>-2.450565024832181</v>
       </c>
       <c r="E14" t="n">
-        <v>2.811556023319517</v>
+        <v>2.81155590100755</v>
       </c>
       <c r="F14" t="n">
         <v>0.7794068643785405</v>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.025686565000691</v>
+        <v>2.02568405177562</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.785476845096756</v>
+        <v>-0.7854835806610089</v>
       </c>
       <c r="E15" t="n">
-        <v>5.508151173976821</v>
+        <v>5.508151625137726</v>
       </c>
       <c r="F15" t="n">
         <v>0.2175941352882373</v>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.6206133918945544</v>
+        <v>-0.6206161169488964</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.380804070854872</v>
+        <v>-1.380808602803271</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1824933171558452</v>
+        <v>0.1824829391149646</v>
       </c>
       <c r="F16" t="n">
         <v>0.1262912362545818</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.127538720618301</v>
+        <v>1.12753897636796</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8084433820549483</v>
+        <v>0.8084420079854822</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6514345194004361</v>
+        <v>0.6514259954623608</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5302395714140973</v>
+        <v>0.5302384766181225</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3889832476002018</v>
+        <v>0.3889820520564337</v>
       </c>
     </row>
     <row r="3">
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.30533136045785</v>
+        <v>-1.305331344212691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5676104278891555</v>
+        <v>0.5676078566580229</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5471899092781141</v>
+        <v>0.5471935398643858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6700423661477959</v>
+        <v>0.6700477747050693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3651939504057284</v>
+        <v>0.3651918912131976</v>
       </c>
     </row>
     <row r="4">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-35.01784671469801</v>
+        <v>-35.01782900696183</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6113638793469639</v>
+        <v>-0.6113553025235018</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1579083435101936</v>
+        <v>0.1579160037899428</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.355644198852895</v>
+        <v>-1.355636277070551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9858073423002829</v>
+        <v>0.9858080081620939</v>
       </c>
     </row>
   </sheetData>
